--- a/docs/people/Scag-Scapes-Ned-Proforma.xlsx
+++ b/docs/people/Scag-Scapes-Ned-Proforma.xlsx
@@ -1281,49 +1281,49 @@
         <v>20</v>
       </c>
       <c r="B6" s="10" t="n">
-        <v>242146.07309104</v>
+        <v>164146.07309104</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>231726.24221904</v>
+        <v>153726.24221904</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>289218.979335931</v>
+        <v>211218.979335931</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>415332.012318055</v>
+        <v>337332.012318055</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>407969.659557169</v>
+        <v>329969.659557169</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>394088.769207364</v>
+        <v>316088.769207364</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>525197.758851492</v>
+        <v>447197.758851492</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>663647.486330165</v>
+        <v>585647.486330165</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>809486.5874483</v>
+        <v>731486.5874483</v>
       </c>
       <c r="K6" s="10" t="n">
-        <v>826428.470548401</v>
+        <v>748428.470548401</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>990695.917051482</v>
+        <v>912695.917051482</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>1162746.42040954</v>
+        <v>1084746.42040954</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>1342609.86275326</v>
+        <v>1264609.86275326</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>1408797.94885832</v>
+        <v>1330797.94885832</v>
       </c>
       <c r="P6" s="10" t="n">
-        <v>1472843.49387317</v>
+        <v>1394843.49387317</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="6" t="s">
@@ -1403,63 +1403,63 @@
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">MAX(0,B6-'Your numbers'!$B$9)</f>
-        <v>242146.07309104</v>
+        <v>164146.07309104</v>
       </c>
       <c r="C8" s="11" t="n">
         <f aca="false">MAX(0,C6-'Your numbers'!$B$9)</f>
-        <v>231726.24221904</v>
+        <v>153726.24221904</v>
       </c>
       <c r="D8" s="11" t="n">
         <f aca="false">MAX(0,D6-'Your numbers'!$B$9)</f>
-        <v>289218.979335931</v>
+        <v>211218.979335931</v>
       </c>
       <c r="E8" s="11" t="n">
         <f aca="false">MAX(0,E6-'Your numbers'!$B$9)</f>
-        <v>415332.012318055</v>
+        <v>337332.012318055</v>
       </c>
       <c r="F8" s="11" t="n">
         <f aca="false">MAX(0,F6-'Your numbers'!$B$9)</f>
-        <v>407969.659557169</v>
+        <v>329969.659557169</v>
       </c>
       <c r="G8" s="11" t="n">
         <f aca="false">MAX(0,G6-'Your numbers'!$B$9)</f>
-        <v>394088.769207364</v>
+        <v>316088.769207364</v>
       </c>
       <c r="H8" s="11" t="n">
         <f aca="false">MAX(0,H6-'Your numbers'!$B$9)</f>
-        <v>525197.758851492</v>
+        <v>447197.758851492</v>
       </c>
       <c r="I8" s="11" t="n">
         <f aca="false">MAX(0,I6-'Your numbers'!$B$9)</f>
-        <v>663647.486330165</v>
+        <v>585647.486330165</v>
       </c>
       <c r="J8" s="11" t="n">
         <f aca="false">MAX(0,J6-'Your numbers'!$B$9)</f>
-        <v>809486.5874483</v>
+        <v>731486.5874483</v>
       </c>
       <c r="K8" s="11" t="n">
         <f aca="false">MAX(0,K6-'Your numbers'!$B$9)</f>
-        <v>826428.470548401</v>
+        <v>748428.470548401</v>
       </c>
       <c r="L8" s="11" t="n">
         <f aca="false">MAX(0,L6-'Your numbers'!$B$9)</f>
-        <v>990695.917051482</v>
+        <v>912695.917051482</v>
       </c>
       <c r="M8" s="11" t="n">
         <f aca="false">MAX(0,M6-'Your numbers'!$B$9)</f>
-        <v>1162746.42040954</v>
+        <v>1084746.42040954</v>
       </c>
       <c r="N8" s="11" t="n">
         <f aca="false">MAX(0,N6-'Your numbers'!$B$9)</f>
-        <v>1342609.86275326</v>
+        <v>1264609.86275326</v>
       </c>
       <c r="O8" s="11" t="n">
         <f aca="false">MAX(0,O6-'Your numbers'!$B$9)</f>
-        <v>1408797.94885832</v>
+        <v>1330797.94885832</v>
       </c>
       <c r="P8" s="11" t="n">
         <f aca="false">MAX(0,P6-'Your numbers'!$B$9)</f>
-        <v>1472843.49387317</v>
+        <v>1394843.49387317</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -1470,63 +1470,63 @@
       </c>
       <c r="B9" s="11" t="n">
         <f aca="false">B8*'Your numbers'!$B$8</f>
-        <v>24214.607309104</v>
+        <v>16414.607309104</v>
       </c>
       <c r="C9" s="11" t="n">
         <f aca="false">C8*'Your numbers'!$B$8</f>
-        <v>23172.624221904</v>
+        <v>15372.624221904</v>
       </c>
       <c r="D9" s="11" t="n">
         <f aca="false">D8*'Your numbers'!$B$8</f>
-        <v>28921.8979335931</v>
+        <v>21121.8979335931</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">E8*'Your numbers'!$B$8</f>
-        <v>41533.2012318055</v>
+        <v>33733.2012318055</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">F8*'Your numbers'!$B$8</f>
-        <v>40796.9659557169</v>
+        <v>32996.9659557169</v>
       </c>
       <c r="G9" s="11" t="n">
         <f aca="false">G8*'Your numbers'!$B$8</f>
-        <v>39408.8769207364</v>
+        <v>31608.8769207364</v>
       </c>
       <c r="H9" s="11" t="n">
         <f aca="false">H8*'Your numbers'!$B$8</f>
-        <v>52519.7758851492</v>
+        <v>44719.7758851492</v>
       </c>
       <c r="I9" s="11" t="n">
         <f aca="false">I8*'Your numbers'!$B$8</f>
-        <v>66364.7486330165</v>
+        <v>58564.7486330165</v>
       </c>
       <c r="J9" s="11" t="n">
         <f aca="false">J8*'Your numbers'!$B$8</f>
-        <v>80948.65874483</v>
+        <v>73148.65874483</v>
       </c>
       <c r="K9" s="11" t="n">
         <f aca="false">K8*'Your numbers'!$B$8</f>
-        <v>82642.8470548401</v>
+        <v>74842.8470548401</v>
       </c>
       <c r="L9" s="11" t="n">
         <f aca="false">L8*'Your numbers'!$B$8</f>
-        <v>99069.5917051482</v>
+        <v>91269.5917051482</v>
       </c>
       <c r="M9" s="11" t="n">
         <f aca="false">M8*'Your numbers'!$B$8</f>
-        <v>116274.642040954</v>
+        <v>108474.642040954</v>
       </c>
       <c r="N9" s="11" t="n">
         <f aca="false">N8*'Your numbers'!$B$8</f>
-        <v>134260.986275326</v>
+        <v>126460.986275326</v>
       </c>
       <c r="O9" s="11" t="n">
         <f aca="false">O8*'Your numbers'!$B$8</f>
-        <v>140879.794885832</v>
+        <v>133079.794885832</v>
       </c>
       <c r="P9" s="11" t="n">
         <f aca="false">P8*'Your numbers'!$B$8</f>
-        <v>147284.349387317</v>
+        <v>139484.349387317</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
@@ -1537,63 +1537,63 @@
       </c>
       <c r="B10" s="10" t="n">
         <f aca="false">B7+B9</f>
-        <v>84214.607309104</v>
+        <v>76414.607309104</v>
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">C7+C9</f>
-        <v>83172.624221904</v>
+        <v>75372.624221904</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">D7+D9</f>
-        <v>94921.8979335931</v>
+        <v>87121.8979335931</v>
       </c>
       <c r="E10" s="10" t="n">
         <f aca="false">E7+E9</f>
-        <v>113533.201231806</v>
+        <v>105733.201231806</v>
       </c>
       <c r="F10" s="10" t="n">
         <f aca="false">F7+F9</f>
-        <v>112796.965955717</v>
+        <v>104996.965955717</v>
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">G7+G9</f>
-        <v>113388.876920736</v>
+        <v>105588.876920736</v>
       </c>
       <c r="H10" s="10" t="n">
         <f aca="false">H7+H9</f>
-        <v>128534.225885149</v>
+        <v>120734.225885149</v>
       </c>
       <c r="I10" s="10" t="n">
         <f aca="false">I7+I9</f>
-        <v>144469.596008017</v>
+        <v>136669.596008017</v>
       </c>
       <c r="J10" s="10" t="n">
         <f aca="false">J7+J9</f>
-        <v>161201.389422643</v>
+        <v>153401.389422643</v>
       </c>
       <c r="K10" s="10" t="n">
         <f aca="false">K7+K9</f>
-        <v>165102.527826293</v>
+        <v>157302.527826293</v>
       </c>
       <c r="L10" s="10" t="n">
         <f aca="false">L7+L9</f>
-        <v>183796.913697816</v>
+        <v>175996.913697816</v>
       </c>
       <c r="M10" s="10" t="n">
         <f aca="false">M7+M9</f>
-        <v>203331.96538842</v>
+        <v>195531.96538842</v>
       </c>
       <c r="N10" s="10" t="n">
         <f aca="false">N7+N9</f>
-        <v>223712.386014847</v>
+        <v>215912.386014847</v>
       </c>
       <c r="O10" s="10" t="n">
         <f aca="false">O7+O9</f>
-        <v>232791.10811819</v>
+        <v>224991.10811819</v>
       </c>
       <c r="P10" s="10" t="n">
         <f aca="false">P7+P9</f>
-        <v>241723.223733565</v>
+        <v>233923.223733565</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -1604,63 +1604,63 @@
       </c>
       <c r="B11" s="10" t="n">
         <f aca="false">B10</f>
-        <v>84214.607309104</v>
+        <v>76414.607309104</v>
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">B11+C10</f>
-        <v>167387.231531008</v>
+        <v>151787.231531008</v>
       </c>
       <c r="D11" s="10" t="n">
         <f aca="false">C11+D10</f>
-        <v>262309.129464601</v>
+        <v>238909.129464601</v>
       </c>
       <c r="E11" s="10" t="n">
         <f aca="false">D11+E10</f>
-        <v>375842.330696407</v>
+        <v>344642.330696407</v>
       </c>
       <c r="F11" s="10" t="n">
         <f aca="false">E11+F10</f>
-        <v>488639.296652124</v>
+        <v>449639.296652124</v>
       </c>
       <c r="G11" s="10" t="n">
         <f aca="false">F11+G10</f>
-        <v>602028.17357286</v>
+        <v>555228.17357286</v>
       </c>
       <c r="H11" s="10" t="n">
         <f aca="false">G11+H10</f>
-        <v>730562.399458009</v>
+        <v>675962.399458009</v>
       </c>
       <c r="I11" s="10" t="n">
         <f aca="false">H11+I10</f>
-        <v>875031.995466026</v>
+        <v>812631.995466026</v>
       </c>
       <c r="J11" s="10" t="n">
         <f aca="false">I11+J10</f>
-        <v>1036233.38488867</v>
+        <v>966033.384888668</v>
       </c>
       <c r="K11" s="10" t="n">
         <f aca="false">J11+K10</f>
-        <v>1201335.91271496</v>
+        <v>1123335.91271496</v>
       </c>
       <c r="L11" s="10" t="n">
         <f aca="false">K11+L10</f>
-        <v>1385132.82641278</v>
+        <v>1299332.82641278</v>
       </c>
       <c r="M11" s="10" t="n">
         <f aca="false">L11+M10</f>
-        <v>1588464.7918012</v>
+        <v>1494864.7918012</v>
       </c>
       <c r="N11" s="10" t="n">
         <f aca="false">M11+N10</f>
-        <v>1812177.17781604</v>
+        <v>1710777.17781604</v>
       </c>
       <c r="O11" s="10" t="n">
         <f aca="false">N11+O10</f>
-        <v>2044968.28593423</v>
+        <v>1935768.28593423</v>
       </c>
       <c r="P11" s="10" t="n">
         <f aca="false">O11+P10</f>
-        <v>2286691.5096678</v>
+        <v>2169691.5096678</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
@@ -1671,63 +1671,63 @@
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">B10/1107883.476</f>
-        <v>0.0760139573641443</v>
+        <v>0.0689735057562173</v>
       </c>
       <c r="C12" s="12" t="n">
         <f aca="false">C10/1130224.27392</f>
-        <v>0.0735894867426915</v>
+        <v>0.0666882015907217</v>
       </c>
       <c r="D12" s="12" t="n">
         <f aca="false">D10/1470581.13731659</f>
-        <v>0.0645472021399647</v>
+        <v>0.0592431765394236</v>
       </c>
       <c r="E12" s="12" t="n">
         <f aca="false">E10/2128361.5241759</f>
-        <v>0.053343005848485</v>
+        <v>0.0496782149229771</v>
       </c>
       <c r="F12" s="12" t="n">
         <f aca="false">F10/2531696.60117519</f>
-        <v>0.0445539034587942</v>
+        <v>0.0414729655626896</v>
       </c>
       <c r="G12" s="12" t="n">
         <f aca="false">G10/2960567.60023987</f>
-        <v>0.0382997087827177</v>
+        <v>0.0356650788558861</v>
       </c>
       <c r="H12" s="12" t="n">
         <f aca="false">H10/3415973.30476096</f>
-        <v>0.0376274093553385</v>
+        <v>0.0353440191458399</v>
       </c>
       <c r="I12" s="12" t="n">
         <f aca="false">I10/3898958.3702101</f>
-        <v>0.0370533825423306</v>
+        <v>0.0350528482305011</v>
       </c>
       <c r="J12" s="12" t="n">
         <f aca="false">J10/4410614.70976327</f>
-        <v>0.0365485085482098</v>
+        <v>0.0347800475709374</v>
       </c>
       <c r="K12" s="12" t="n">
         <f aca="false">K10/4952082.94628947</f>
-        <v>0.0333400166388573</v>
+        <v>0.0317649218586206</v>
       </c>
       <c r="L12" s="12" t="n">
         <f aca="false">L10/5524553.93215493</f>
-        <v>0.033269095741477</v>
+        <v>0.031857217045787</v>
       </c>
       <c r="M12" s="12" t="n">
         <f aca="false">M10/6129270.33838766</f>
-        <v>0.0331739267747664</v>
+        <v>0.0319013446288707</v>
       </c>
       <c r="N12" s="12" t="n">
         <f aca="false">N10/6767528.314843</f>
-        <v>0.033056734395065</v>
+        <v>0.031904171799517</v>
       </c>
       <c r="O12" s="12" t="n">
         <f aca="false">O10/7045784.99129078</f>
-        <v>0.0330397689407128</v>
+        <v>0.0319327240891255</v>
       </c>
       <c r="P12" s="12" t="n">
         <f aca="false">P10/7328447.27269707</f>
-        <v>0.0329842345504935</v>
+        <v>0.0319198890336663</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="6" t="s">
@@ -1761,49 +1761,49 @@
         <v>30</v>
       </c>
       <c r="B14" s="11" t="n">
-        <v>722514.397345807</v>
+        <v>691314.397345807</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>814784.283227823</v>
+        <v>752384.283227823</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1019423.92033104</v>
+        <v>925823.920331045</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1867217.68455785</v>
+        <v>1742417.68455785</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1982323.55921217</v>
+        <v>1826323.55921217</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>2066998.57190214</v>
+        <v>1879798.57190215</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>2784973.43382394</v>
+        <v>2566573.43382394</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>3588363.68812422</v>
+        <v>3338763.68812422</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>4480151.48996621</v>
+        <v>4199351.48996621</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>4863505.48237858</v>
+        <v>4551505.48237858</v>
       </c>
       <c r="L14" s="11" t="n">
-        <v>7857544.27315891</v>
+        <v>7514344.27315891</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>9340457.46435439</v>
+        <v>8966057.46435439</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>10942353.2656805</v>
+        <v>10536753.2656805</v>
       </c>
       <c r="O14" s="11" t="n">
-        <v>11949731.8634761</v>
+        <v>11512931.8634761</v>
       </c>
       <c r="P14" s="11" t="n">
-        <v>12958190.7073309</v>
+        <v>12490190.7073309</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -1814,63 +1814,63 @@
       </c>
       <c r="B15" s="11" t="n">
         <f aca="false">MAX(0,B14-'Your numbers'!$B$11)</f>
-        <v>552514.397345807</v>
+        <v>521314.397345807</v>
       </c>
       <c r="C15" s="11" t="n">
         <f aca="false">MAX(0,C14-'Your numbers'!$B$11)</f>
-        <v>644784.283227823</v>
+        <v>582384.283227823</v>
       </c>
       <c r="D15" s="11" t="n">
         <f aca="false">MAX(0,D14-'Your numbers'!$B$11)</f>
-        <v>849423.92033104</v>
+        <v>755823.920331045</v>
       </c>
       <c r="E15" s="11" t="n">
         <f aca="false">MAX(0,E14-'Your numbers'!$B$11)</f>
-        <v>1697217.68455785</v>
+        <v>1572417.68455785</v>
       </c>
       <c r="F15" s="11" t="n">
         <f aca="false">MAX(0,F14-'Your numbers'!$B$11)</f>
-        <v>1812323.55921217</v>
+        <v>1656323.55921217</v>
       </c>
       <c r="G15" s="11" t="n">
         <f aca="false">MAX(0,G14-'Your numbers'!$B$11)</f>
-        <v>1896998.57190214</v>
+        <v>1709798.57190215</v>
       </c>
       <c r="H15" s="11" t="n">
         <f aca="false">MAX(0,H14-'Your numbers'!$B$11)</f>
-        <v>2614973.43382394</v>
+        <v>2396573.43382394</v>
       </c>
       <c r="I15" s="11" t="n">
         <f aca="false">MAX(0,I14-'Your numbers'!$B$11)</f>
-        <v>3418363.68812422</v>
+        <v>3168763.68812422</v>
       </c>
       <c r="J15" s="11" t="n">
         <f aca="false">MAX(0,J14-'Your numbers'!$B$11)</f>
-        <v>4310151.48996621</v>
+        <v>4029351.48996621</v>
       </c>
       <c r="K15" s="11" t="n">
         <f aca="false">MAX(0,K14-'Your numbers'!$B$11)</f>
-        <v>4693505.48237858</v>
+        <v>4381505.48237858</v>
       </c>
       <c r="L15" s="11" t="n">
         <f aca="false">MAX(0,L14-'Your numbers'!$B$11)</f>
-        <v>7687544.27315891</v>
+        <v>7344344.27315891</v>
       </c>
       <c r="M15" s="11" t="n">
         <f aca="false">MAX(0,M14-'Your numbers'!$B$11)</f>
-        <v>9170457.46435439</v>
+        <v>8796057.46435439</v>
       </c>
       <c r="N15" s="11" t="n">
         <f aca="false">MAX(0,N14-'Your numbers'!$B$11)</f>
-        <v>10772353.2656805</v>
+        <v>10366753.2656805</v>
       </c>
       <c r="O15" s="11" t="n">
         <f aca="false">MAX(0,O14-'Your numbers'!$B$11)</f>
-        <v>11779731.8634761</v>
+        <v>11342931.8634761</v>
       </c>
       <c r="P15" s="11" t="n">
         <f aca="false">MAX(0,P14-'Your numbers'!$B$11)</f>
-        <v>12788190.7073309</v>
+        <v>12320190.7073309</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -1881,63 +1881,63 @@
       </c>
       <c r="B16" s="10" t="n">
         <f aca="false">B15*'Your numbers'!$B$10</f>
-        <v>82877.1596018711</v>
+        <v>78197.1596018711</v>
       </c>
       <c r="C16" s="10" t="n">
         <f aca="false">C15*'Your numbers'!$B$10</f>
-        <v>96717.6424841734</v>
+        <v>87357.6424841734</v>
       </c>
       <c r="D16" s="10" t="n">
         <f aca="false">D15*'Your numbers'!$B$10</f>
-        <v>127413.588049656</v>
+        <v>113373.588049657</v>
       </c>
       <c r="E16" s="10" t="n">
         <f aca="false">E15*'Your numbers'!$B$10</f>
-        <v>254582.652683678</v>
+        <v>235862.652683678</v>
       </c>
       <c r="F16" s="10" t="n">
         <f aca="false">F15*'Your numbers'!$B$10</f>
-        <v>271848.533881826</v>
+        <v>248448.533881826</v>
       </c>
       <c r="G16" s="10" t="n">
         <f aca="false">G15*'Your numbers'!$B$10</f>
-        <v>284549.785785321</v>
+        <v>256469.785785322</v>
       </c>
       <c r="H16" s="10" t="n">
         <f aca="false">H15*'Your numbers'!$B$10</f>
-        <v>392246.015073591</v>
+        <v>359486.015073591</v>
       </c>
       <c r="I16" s="10" t="n">
         <f aca="false">I15*'Your numbers'!$B$10</f>
-        <v>512754.553218633</v>
+        <v>475314.553218633</v>
       </c>
       <c r="J16" s="10" t="n">
         <f aca="false">J15*'Your numbers'!$B$10</f>
-        <v>646522.723494932</v>
+        <v>604402.723494932</v>
       </c>
       <c r="K16" s="10" t="n">
         <f aca="false">K15*'Your numbers'!$B$10</f>
-        <v>704025.822356787</v>
+        <v>657225.822356787</v>
       </c>
       <c r="L16" s="10" t="n">
         <f aca="false">L15*'Your numbers'!$B$10</f>
-        <v>1153131.64097384</v>
+        <v>1101651.64097384</v>
       </c>
       <c r="M16" s="10" t="n">
         <f aca="false">M15*'Your numbers'!$B$10</f>
-        <v>1375568.61965316</v>
+        <v>1319408.61965316</v>
       </c>
       <c r="N16" s="10" t="n">
         <f aca="false">N15*'Your numbers'!$B$10</f>
-        <v>1615852.98985207</v>
+        <v>1555012.98985207</v>
       </c>
       <c r="O16" s="10" t="n">
         <f aca="false">O15*'Your numbers'!$B$10</f>
-        <v>1766959.77952141</v>
+        <v>1701439.77952141</v>
       </c>
       <c r="P16" s="10" t="n">
         <f aca="false">P15*'Your numbers'!$B$10</f>
-        <v>1918228.60609964</v>
+        <v>1848028.60609964</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="6" t="s">
@@ -1950,63 +1950,63 @@
       </c>
       <c r="B17" s="10" t="n">
         <f aca="false">B11+B16</f>
-        <v>167091.766910975</v>
+        <v>154611.766910975</v>
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">C11+C16</f>
-        <v>264104.874015181</v>
+        <v>239144.874015181</v>
       </c>
       <c r="D17" s="10" t="n">
         <f aca="false">D11+D16</f>
-        <v>389722.717514257</v>
+        <v>352282.717514258</v>
       </c>
       <c r="E17" s="10" t="n">
         <f aca="false">E11+E16</f>
-        <v>630424.983380084</v>
+        <v>580504.983380084</v>
       </c>
       <c r="F17" s="10" t="n">
         <f aca="false">F11+F16</f>
-        <v>760487.830533949</v>
+        <v>698087.830533949</v>
       </c>
       <c r="G17" s="10" t="n">
         <f aca="false">G11+G16</f>
-        <v>886577.959358181</v>
+        <v>811697.959358183</v>
       </c>
       <c r="H17" s="10" t="n">
         <f aca="false">H11+H16</f>
-        <v>1122808.4145316</v>
+        <v>1035448.4145316</v>
       </c>
       <c r="I17" s="10" t="n">
         <f aca="false">I11+I16</f>
-        <v>1387786.54868466</v>
+        <v>1287946.54868466</v>
       </c>
       <c r="J17" s="10" t="n">
         <f aca="false">J11+J16</f>
-        <v>1682756.1083836</v>
+        <v>1570436.1083836</v>
       </c>
       <c r="K17" s="10" t="n">
         <f aca="false">K11+K16</f>
-        <v>1905361.73507175</v>
+        <v>1780561.73507175</v>
       </c>
       <c r="L17" s="10" t="n">
         <f aca="false">L11+L16</f>
-        <v>2538264.46738661</v>
+        <v>2400984.46738661</v>
       </c>
       <c r="M17" s="10" t="n">
         <f aca="false">M11+M16</f>
-        <v>2964033.41145435</v>
+        <v>2814273.41145435</v>
       </c>
       <c r="N17" s="10" t="n">
         <f aca="false">N11+N16</f>
-        <v>3428030.16766812</v>
+        <v>3265790.16766812</v>
       </c>
       <c r="O17" s="10" t="n">
         <f aca="false">O11+O16</f>
-        <v>3811928.06545565</v>
+        <v>3637208.06545565</v>
       </c>
       <c r="P17" s="10" t="n">
         <f aca="false">P11+P16</f>
-        <v>4204920.11576743</v>
+        <v>4017720.11576743</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="6" t="s">
@@ -2413,49 +2413,49 @@
         <v>44</v>
       </c>
       <c r="B11" s="11" t="n">
-        <v>94158.4292364159</v>
+        <v>62958.4292364159</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>186848.926124032</v>
+        <v>124448.926124032</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>288686.517858404</v>
+        <v>195086.517858404</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>427119.322785626</v>
+        <v>302319.322785626</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>576457.186608494</v>
+        <v>420457.186608494</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>720242.694291439</v>
+        <v>533042.694291439</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>916471.797832036</v>
+        <v>698071.797832036</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>1168080.7923641</v>
+        <v>918480.792364102</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>1478025.42734342</v>
+        <v>1197225.42734342</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>1794746.81556278</v>
+        <v>1482746.81556278</v>
       </c>
       <c r="L11" s="11" t="n">
-        <v>2177175.18238338</v>
+        <v>1833975.18238338</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>2628423.75054719</v>
+        <v>2254023.75054719</v>
       </c>
       <c r="N11" s="11" t="n">
-        <v>3151617.69564849</v>
+        <v>2746017.69564849</v>
       </c>
       <c r="O11" s="11" t="n">
-        <v>3715136.87519182</v>
+        <v>3278336.87519182</v>
       </c>
       <c r="P11" s="11" t="n">
-        <v>4304274.27274109</v>
+        <v>3836274.27274109</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
@@ -2465,49 +2465,49 @@
         <v>30</v>
       </c>
       <c r="B12" s="10" t="n">
-        <v>722514.397345807</v>
+        <v>691314.397345807</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>814784.283227823</v>
+        <v>752384.283227823</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1019423.92033104</v>
+        <v>925823.920331045</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1867217.68455785</v>
+        <v>1742417.68455785</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1982323.55921217</v>
+        <v>1826323.55921217</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>2066998.57190214</v>
+        <v>1879798.57190215</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>2784973.43382394</v>
+        <v>2566573.43382394</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>3588363.68812422</v>
+        <v>3338763.68812422</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>4480151.48996621</v>
+        <v>4199351.48996621</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>4863505.48237858</v>
+        <v>4551505.48237858</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>7857544.27315891</v>
+        <v>7514344.27315891</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>9340457.46435439</v>
+        <v>8966057.46435439</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>10942353.2656805</v>
+        <v>10536753.2656805</v>
       </c>
       <c r="O12" s="10" t="n">
-        <v>11949731.8634761</v>
+        <v>11512931.8634761</v>
       </c>
       <c r="P12" s="10" t="n">
-        <v>12958190.7073309</v>
+        <v>12490190.7073309</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="6" t="s">
@@ -2755,63 +2755,63 @@
       </c>
       <c r="B9" s="10" t="n">
         <f aca="false">'Year by year'!B16</f>
-        <v>82877.1596018711</v>
+        <v>78197.1596018711</v>
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">'Year by year'!C16</f>
-        <v>96717.6424841734</v>
+        <v>87357.6424841734</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">'Year by year'!D16</f>
-        <v>127413.588049656</v>
+        <v>113373.588049657</v>
       </c>
       <c r="E9" s="10" t="n">
         <f aca="false">'Year by year'!E16</f>
-        <v>254582.652683678</v>
+        <v>235862.652683678</v>
       </c>
       <c r="F9" s="10" t="n">
         <f aca="false">'Year by year'!F16</f>
-        <v>271848.533881826</v>
+        <v>248448.533881826</v>
       </c>
       <c r="G9" s="10" t="n">
         <f aca="false">'Year by year'!G16</f>
-        <v>284549.785785321</v>
+        <v>256469.785785322</v>
       </c>
       <c r="H9" s="10" t="n">
         <f aca="false">'Year by year'!H16</f>
-        <v>392246.015073591</v>
+        <v>359486.015073591</v>
       </c>
       <c r="I9" s="10" t="n">
         <f aca="false">'Year by year'!I16</f>
-        <v>512754.553218633</v>
+        <v>475314.553218633</v>
       </c>
       <c r="J9" s="10" t="n">
         <f aca="false">'Year by year'!J16</f>
-        <v>646522.723494932</v>
+        <v>604402.723494932</v>
       </c>
       <c r="K9" s="10" t="n">
         <f aca="false">'Year by year'!K16</f>
-        <v>704025.822356787</v>
+        <v>657225.822356787</v>
       </c>
       <c r="L9" s="10" t="n">
         <f aca="false">'Year by year'!L16</f>
-        <v>1153131.64097384</v>
+        <v>1101651.64097384</v>
       </c>
       <c r="M9" s="10" t="n">
         <f aca="false">'Year by year'!M16</f>
-        <v>1375568.61965316</v>
+        <v>1319408.61965316</v>
       </c>
       <c r="N9" s="10" t="n">
         <f aca="false">'Year by year'!N16</f>
-        <v>1615852.98985207</v>
+        <v>1555012.98985207</v>
       </c>
       <c r="O9" s="10" t="n">
         <f aca="false">'Year by year'!O16</f>
-        <v>1766959.77952141</v>
+        <v>1701439.77952141</v>
       </c>
       <c r="P9" s="10" t="n">
         <f aca="false">'Year by year'!P16</f>
-        <v>1918228.60609964</v>
+        <v>1848028.60609964</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="6" t="s">
@@ -2824,63 +2824,63 @@
       </c>
       <c r="B10" s="10" t="n">
         <f aca="false">B9*(1-$B$4)</f>
-        <v>66301.7276814969</v>
+        <v>62557.7276814969</v>
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">C9*(1-$B$4)</f>
-        <v>77374.1139873388</v>
+        <v>69886.1139873388</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">D9*(1-$B$4)</f>
-        <v>101930.870439725</v>
+        <v>90698.8704397254</v>
       </c>
       <c r="E10" s="10" t="n">
         <f aca="false">E9*(1-$B$4)</f>
-        <v>203666.122146942</v>
+        <v>188690.122146942</v>
       </c>
       <c r="F10" s="10" t="n">
         <f aca="false">F9*(1-$B$4)</f>
-        <v>217478.82710546</v>
+        <v>198758.82710546</v>
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">G9*(1-$B$4)</f>
-        <v>227639.828628257</v>
+        <v>205175.828628258</v>
       </c>
       <c r="H10" s="10" t="n">
         <f aca="false">H9*(1-$B$4)</f>
-        <v>313796.812058873</v>
+        <v>287588.812058873</v>
       </c>
       <c r="I10" s="10" t="n">
         <f aca="false">I9*(1-$B$4)</f>
-        <v>410203.642574906</v>
+        <v>380251.642574906</v>
       </c>
       <c r="J10" s="10" t="n">
         <f aca="false">J9*(1-$B$4)</f>
-        <v>517218.178795945</v>
+        <v>483522.178795945</v>
       </c>
       <c r="K10" s="10" t="n">
         <f aca="false">K9*(1-$B$4)</f>
-        <v>563220.65788543</v>
+        <v>525780.65788543</v>
       </c>
       <c r="L10" s="10" t="n">
         <f aca="false">L9*(1-$B$4)</f>
-        <v>922505.312779069</v>
+        <v>881321.312779069</v>
       </c>
       <c r="M10" s="10" t="n">
         <f aca="false">M9*(1-$B$4)</f>
-        <v>1100454.89572253</v>
+        <v>1055526.89572253</v>
       </c>
       <c r="N10" s="10" t="n">
         <f aca="false">N9*(1-$B$4)</f>
-        <v>1292682.39188166</v>
+        <v>1244010.39188166</v>
       </c>
       <c r="O10" s="10" t="n">
         <f aca="false">O9*(1-$B$4)</f>
-        <v>1413567.82361713</v>
+        <v>1361151.82361713</v>
       </c>
       <c r="P10" s="10" t="n">
         <f aca="false">P9*(1-$B$4)</f>
-        <v>1534582.88487971</v>
+        <v>1478422.88487971</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -2891,63 +2891,63 @@
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">B10</f>
-        <v>66301.7276814969</v>
+        <v>62557.7276814969</v>
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">C10</f>
-        <v>77374.1139873388</v>
+        <v>69886.1139873388</v>
       </c>
       <c r="D11" s="11" t="n">
         <f aca="false">D10</f>
-        <v>101930.870439725</v>
+        <v>90698.8704397254</v>
       </c>
       <c r="E11" s="11" t="n">
         <f aca="false">E10</f>
-        <v>203666.122146942</v>
+        <v>188690.122146942</v>
       </c>
       <c r="F11" s="11" t="n">
         <f aca="false">F10</f>
-        <v>217478.82710546</v>
+        <v>198758.82710546</v>
       </c>
       <c r="G11" s="11" t="n">
         <f aca="false">G10</f>
-        <v>227639.828628257</v>
+        <v>205175.828628258</v>
       </c>
       <c r="H11" s="11" t="n">
         <f aca="false">H10</f>
-        <v>313796.812058873</v>
+        <v>287588.812058873</v>
       </c>
       <c r="I11" s="11" t="n">
         <f aca="false">I10</f>
-        <v>410203.642574906</v>
+        <v>380251.642574906</v>
       </c>
       <c r="J11" s="11" t="n">
         <f aca="false">J10</f>
-        <v>517218.178795945</v>
+        <v>483522.178795945</v>
       </c>
       <c r="K11" s="11" t="n">
         <f aca="false">K10</f>
-        <v>563220.65788543</v>
+        <v>525780.65788543</v>
       </c>
       <c r="L11" s="11" t="n">
         <f aca="false">L10</f>
-        <v>922505.312779069</v>
+        <v>881321.312779069</v>
       </c>
       <c r="M11" s="11" t="n">
         <f aca="false">M10</f>
-        <v>1100454.89572253</v>
+        <v>1055526.89572253</v>
       </c>
       <c r="N11" s="11" t="n">
         <f aca="false">N10</f>
-        <v>1292682.39188166</v>
+        <v>1244010.39188166</v>
       </c>
       <c r="O11" s="11" t="n">
         <f aca="false">O10</f>
-        <v>1413567.82361713</v>
+        <v>1361151.82361713</v>
       </c>
       <c r="P11" s="11" t="n">
         <f aca="false">P10</f>
-        <v>1534582.88487971</v>
+        <v>1478422.88487971</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
@@ -2958,63 +2958,63 @@
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,36,-B10))</f>
-        <v>2100.67126775031</v>
+        <v>1982.04821671552</v>
       </c>
       <c r="C12" s="11" t="n">
         <f aca="false">IF(C10=0,0,PMT($B$5/12,36,-C10))</f>
-        <v>2451.48329922329</v>
+        <v>2214.2371971537</v>
       </c>
       <c r="D12" s="11" t="n">
         <f aca="false">IF(D10=0,0,PMT($B$5/12,36,-D10))</f>
-        <v>3229.52746960266</v>
+        <v>2873.6583164983</v>
       </c>
       <c r="E12" s="11" t="n">
         <f aca="false">IF(E10=0,0,PMT($B$5/12,36,-E10))</f>
-        <v>6452.85705168139</v>
+        <v>5978.36484754222</v>
       </c>
       <c r="F12" s="11" t="n">
         <f aca="false">IF(F10=0,0,PMT($B$5/12,36,-F10))</f>
-        <v>6890.49198897383</v>
+        <v>6297.37673379986</v>
       </c>
       <c r="G12" s="11" t="n">
         <f aca="false">IF(G10=0,0,PMT($B$5/12,36,-G10))</f>
-        <v>7212.42815409223</v>
+        <v>6500.68984788351</v>
       </c>
       <c r="H12" s="11" t="n">
         <f aca="false">IF(H10=0,0,PMT($B$5/12,36,-H10))</f>
-        <v>9942.18356074121</v>
+        <v>9111.82220349766</v>
       </c>
       <c r="I12" s="11" t="n">
         <f aca="false">IF(I10=0,0,PMT($B$5/12,36,-I10))</f>
-        <v>12996.6900715334</v>
+        <v>12047.7056632551</v>
       </c>
       <c r="J12" s="11" t="n">
         <f aca="false">IF(J10=0,0,PMT($B$5/12,36,-J10))</f>
-        <v>16387.2859026267</v>
+        <v>15319.6784433135</v>
       </c>
       <c r="K12" s="11" t="n">
         <f aca="false">IF(K10=0,0,PMT($B$5/12,36,-K10))</f>
-        <v>17844.8057810345</v>
+        <v>16658.5752706866</v>
       </c>
       <c r="L12" s="11" t="n">
         <f aca="false">IF(L10=0,0,PMT($B$5/12,36,-L10))</f>
-        <v>29228.2037386911</v>
+        <v>27923.3501773084</v>
       </c>
       <c r="M12" s="11" t="n">
         <f aca="false">IF(M10=0,0,PMT($B$5/12,36,-M10))</f>
-        <v>34866.2706348241</v>
+        <v>33442.7940224066</v>
       </c>
       <c r="N12" s="11" t="n">
         <f aca="false">IF(N10=0,0,PMT($B$5/12,36,-N10))</f>
-        <v>40956.7118974243</v>
+        <v>39414.612233972</v>
       </c>
       <c r="O12" s="11" t="n">
         <f aca="false">IF(O10=0,0,PMT($B$5/12,36,-O10))</f>
-        <v>44786.7863467085</v>
+        <v>43126.0636322214</v>
       </c>
       <c r="P12" s="11" t="n">
         <f aca="false">IF(P10=0,0,PMT($B$5/12,36,-P10))</f>
-        <v>48620.9679140507</v>
+        <v>46841.6221485288</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
@@ -3025,63 +3025,63 @@
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,60,-B10))</f>
-        <v>1368.28418303561</v>
+        <v>1291.0183837808</v>
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">IF(C10=0,0,PMT($B$5/12,60,-C10))</f>
-        <v>1596.78759585047</v>
+        <v>1442.25599734086</v>
       </c>
       <c r="D13" s="10" t="n">
         <f aca="false">IF(D10=0,0,PMT($B$5/12,60,-D10))</f>
-        <v>2103.57109328615</v>
+        <v>1871.77369552175</v>
       </c>
       <c r="E13" s="10" t="n">
         <f aca="false">IF(E10=0,0,PMT($B$5/12,60,-E10))</f>
-        <v>4203.10515726771</v>
+        <v>3894.04196024849</v>
       </c>
       <c r="F13" s="10" t="n">
         <f aca="false">IF(F10=0,0,PMT($B$5/12,60,-F10))</f>
-        <v>4488.16116380904</v>
+        <v>4101.83216753501</v>
       </c>
       <c r="G13" s="10" t="n">
         <f aca="false">IF(G10=0,0,PMT($B$5/12,60,-G10))</f>
-        <v>4697.85611677062</v>
+        <v>4234.26132124181</v>
       </c>
       <c r="H13" s="10" t="n">
         <f aca="false">IF(H10=0,0,PMT($B$5/12,60,-H10))</f>
-        <v>6475.89783315672</v>
+        <v>5935.03723837308</v>
       </c>
       <c r="I13" s="10" t="n">
         <f aca="false">IF(I10=0,0,PMT($B$5/12,60,-I10))</f>
-        <v>8465.4680290552</v>
+        <v>7847.34163501675</v>
       </c>
       <c r="J13" s="10" t="n">
         <f aca="false">IF(J10=0,0,PMT($B$5/12,60,-J10))</f>
-        <v>10673.9519160747</v>
+        <v>9978.55972278141</v>
       </c>
       <c r="K13" s="10" t="n">
         <f aca="false">IF(K10=0,0,PMT($B$5/12,60,-K10))</f>
-        <v>11623.3157821408</v>
+        <v>10850.6577895927</v>
       </c>
       <c r="L13" s="10" t="n">
         <f aca="false">IF(L10=0,0,PMT($B$5/12,60,-L10))</f>
-        <v>19037.9568132155</v>
+        <v>18188.0330214127</v>
       </c>
       <c r="M13" s="10" t="n">
         <f aca="false">IF(M10=0,0,PMT($B$5/12,60,-M10))</f>
-        <v>22710.3437665237</v>
+        <v>21783.154175466</v>
       </c>
       <c r="N13" s="10" t="n">
         <f aca="false">IF(N10=0,0,PMT($B$5/12,60,-N10))</f>
-        <v>26677.3873374332</v>
+        <v>25672.9319471208</v>
       </c>
       <c r="O13" s="10" t="n">
         <f aca="false">IF(O10=0,0,PMT($B$5/12,60,-O10))</f>
-        <v>29172.1281230378</v>
+        <v>28090.4069334705</v>
       </c>
       <c r="P13" s="10" t="n">
         <f aca="false">IF(P10=0,0,PMT($B$5/12,60,-P10))</f>
-        <v>31669.5441033589</v>
+        <v>30510.5571145368</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="6" t="s">
@@ -3094,63 +3094,63 @@
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,84,-B10))</f>
-        <v>1058.34081845174</v>
+        <v>998.577247232027</v>
       </c>
       <c r="C14" s="11" t="n">
         <f aca="false">IF(C10=0,0,PMT($B$5/12,84,-C10))</f>
-        <v>1235.08369974485</v>
+        <v>1115.55655730542</v>
       </c>
       <c r="D14" s="11" t="n">
         <f aca="false">IF(D10=0,0,PMT($B$5/12,84,-D10))</f>
-        <v>1627.07073584725</v>
+        <v>1447.78002218811</v>
       </c>
       <c r="E14" s="11" t="n">
         <f aca="false">IF(E10=0,0,PMT($B$5/12,84,-E10))</f>
-        <v>3251.01890918057</v>
+        <v>3011.96462430171</v>
       </c>
       <c r="F14" s="11" t="n">
         <f aca="false">IF(F10=0,0,PMT($B$5/12,84,-F10))</f>
-        <v>3471.50410590208</v>
+        <v>3172.6862498035</v>
       </c>
       <c r="G14" s="11" t="n">
         <f aca="false">IF(G10=0,0,PMT($B$5/12,84,-G10))</f>
-        <v>3633.69901460167</v>
+        <v>3275.1175872834</v>
       </c>
       <c r="H14" s="11" t="n">
         <f aca="false">IF(H10=0,0,PMT($B$5/12,84,-H10))</f>
-        <v>5008.97920032055</v>
+        <v>4590.63420178254</v>
       </c>
       <c r="I14" s="11" t="n">
         <f aca="false">IF(I10=0,0,PMT($B$5/12,84,-I10))</f>
-        <v>6547.8724913494</v>
+        <v>6069.76392159168</v>
       </c>
       <c r="J14" s="11" t="n">
         <f aca="false">IF(J10=0,0,PMT($B$5/12,84,-J10))</f>
-        <v>8256.09120315252</v>
+        <v>7718.21906217508</v>
       </c>
       <c r="K14" s="11" t="n">
         <f aca="false">IF(K10=0,0,PMT($B$5/12,84,-K10))</f>
-        <v>8990.40542199544</v>
+        <v>8392.76970979828</v>
       </c>
       <c r="L14" s="11" t="n">
         <f aca="false">IF(L10=0,0,PMT($B$5/12,84,-L10))</f>
-        <v>14725.483963899</v>
+        <v>14068.0846804821</v>
       </c>
       <c r="M14" s="11" t="n">
         <f aca="false">IF(M10=0,0,PMT($B$5/12,84,-M10))</f>
-        <v>17566.0028137281</v>
+        <v>16848.8399590915</v>
       </c>
       <c r="N14" s="11" t="n">
         <f aca="false">IF(N10=0,0,PMT($B$5/12,84,-N10))</f>
-        <v>20634.4327435074</v>
+        <v>19857.5063176511</v>
       </c>
       <c r="O14" s="11" t="n">
         <f aca="false">IF(O10=0,0,PMT($B$5/12,84,-O10))</f>
-        <v>22564.0655183335</v>
+        <v>21727.3755212575</v>
       </c>
       <c r="P14" s="11" t="n">
         <f aca="false">IF(P10=0,0,PMT($B$5/12,84,-P10))</f>
-        <v>24495.7675034896</v>
+        <v>23599.3139351938</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -3234,49 +3234,49 @@
         <v>44</v>
       </c>
       <c r="B17" s="11" t="n">
-        <v>94158.4292364159</v>
+        <v>62958.4292364159</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>186848.926124032</v>
+        <v>124448.926124032</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>288686.517858404</v>
+        <v>195086.517858404</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>427119.322785626</v>
+        <v>302319.322785626</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>576457.186608494</v>
+        <v>420457.186608494</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>720242.694291439</v>
+        <v>533042.694291439</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>916471.797832036</v>
+        <v>698071.797832036</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>1168080.7923641</v>
+        <v>918480.792364102</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>1478025.42734342</v>
+        <v>1197225.42734342</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>1794746.81556278</v>
+        <v>1482746.81556278</v>
       </c>
       <c r="L17" s="11" t="n">
-        <v>2177175.18238338</v>
+        <v>1833975.18238338</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>2628423.75054719</v>
+        <v>2254023.75054719</v>
       </c>
       <c r="N17" s="11" t="n">
-        <v>3151617.69564849</v>
+        <v>2746017.69564849</v>
       </c>
       <c r="O17" s="11" t="n">
-        <v>3715136.87519182</v>
+        <v>3278336.87519182</v>
       </c>
       <c r="P17" s="11" t="n">
-        <v>4304274.27274109</v>
+        <v>3836274.27274109</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -3287,63 +3287,63 @@
       </c>
       <c r="B18" s="18" t="n">
         <f aca="false">IF(B16=0,0,B13*12/B16)</f>
-        <v>0.0522668007111103</v>
+        <v>0.0493153406405304</v>
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">IF(C16=0,0,C13*12/C16)</f>
-        <v>0.063087901164585</v>
+        <v>0.0569824715890332</v>
       </c>
       <c r="D18" s="18" t="n">
         <f aca="false">IF(D16=0,0,D13*12/D16)</f>
-        <v>0.0698824108462976</v>
+        <v>0.0621819052463801</v>
       </c>
       <c r="E18" s="18" t="n">
         <f aca="false">IF(E16=0,0,E13*12/E16)</f>
-        <v>0.103496713969808</v>
+        <v>0.0958863820595571</v>
       </c>
       <c r="F18" s="18" t="n">
         <f aca="false">IF(F16=0,0,F13*12/F16)</f>
-        <v>0.112211121876743</v>
+        <v>0.102552286442092</v>
       </c>
       <c r="G18" s="18" t="n">
         <f aca="false">IF(G16=0,0,G13*12/G16)</f>
-        <v>0.120951795292382</v>
+        <v>0.109016005559009</v>
       </c>
       <c r="H18" s="18" t="n">
         <f aca="false">IF(H16=0,0,H13*12/H16)</f>
-        <v>0.130125695962642</v>
+        <v>0.119257726280563</v>
       </c>
       <c r="I18" s="18" t="n">
         <f aca="false">IF(I16=0,0,I13*12/I16)</f>
-        <v>0.138090074711504</v>
+        <v>0.128007097652119</v>
       </c>
       <c r="J18" s="18" t="n">
         <f aca="false">IF(J16=0,0,J13*12/J16)</f>
-        <v>0.145308419681892</v>
+        <v>0.135841790877391</v>
       </c>
       <c r="K18" s="18" t="n">
         <f aca="false">IF(K16=0,0,K13*12/K16)</f>
-        <v>0.155248630200411</v>
+        <v>0.144928503206976</v>
       </c>
       <c r="L18" s="18" t="n">
         <f aca="false">IF(L16=0,0,L13*12/L16)</f>
-        <v>0.214977283805184</v>
+        <v>0.205379914192687</v>
       </c>
       <c r="M18" s="18" t="n">
         <f aca="false">IF(M16=0,0,M13*12/M16)</f>
-        <v>0.220712626247496</v>
+        <v>0.21170164641489</v>
       </c>
       <c r="N18" s="18" t="n">
         <f aca="false">IF(N16=0,0,N13*12/N16)</f>
-        <v>0.226301722106003</v>
+        <v>0.217781023218544</v>
       </c>
       <c r="O18" s="18" t="n">
         <f aca="false">IF(O16=0,0,O13*12/O16)</f>
-        <v>0.236403310624755</v>
+        <v>0.227637324498953</v>
       </c>
       <c r="P18" s="18" t="n">
         <f aca="false">IF(P16=0,0,P13*12/P16)</f>
-        <v>0.246001961200289</v>
+        <v>0.236999208545393</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="6" t="s">

--- a/docs/people/Scag-Scapes-Ned-Proforma.xlsx
+++ b/docs/people/Scag-Scapes-Ned-Proforma.xlsx
@@ -1281,49 +1281,49 @@
         <v>20</v>
       </c>
       <c r="B6" s="10" t="n">
-        <v>164146.07309104</v>
+        <v>159346.07309104</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>153726.24221904</v>
+        <v>148686.24221904</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>211218.979335931</v>
+        <v>205430.854335931</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>337332.012318055</v>
+        <v>330212.618568055</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>329969.659557169</v>
+        <v>321947.318307169</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>316088.769207364</v>
+        <v>364099.926862789</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>447197.758851492</v>
+        <v>496151.297211341</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>585647.486330165</v>
+        <v>635530.442582843</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>731486.5874483</v>
+        <v>719075.961720472</v>
       </c>
       <c r="K6" s="10" t="n">
-        <v>748428.470548401</v>
+        <v>879166.335282246</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>912695.917051482</v>
+        <v>1047070.66564829</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>1084746.42040954</v>
+        <v>1222827.40169565</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>1264609.86275326</v>
+        <v>1406465.40590655</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>1330797.94885832</v>
+        <v>1477343.6700041</v>
       </c>
       <c r="P6" s="10" t="n">
-        <v>1394843.49387317</v>
+        <v>1546229.81094027</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="6" t="s">
@@ -1403,63 +1403,63 @@
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">MAX(0,B6-'Your numbers'!$B$9)</f>
-        <v>164146.07309104</v>
+        <v>159346.07309104</v>
       </c>
       <c r="C8" s="11" t="n">
         <f aca="false">MAX(0,C6-'Your numbers'!$B$9)</f>
-        <v>153726.24221904</v>
+        <v>148686.24221904</v>
       </c>
       <c r="D8" s="11" t="n">
         <f aca="false">MAX(0,D6-'Your numbers'!$B$9)</f>
-        <v>211218.979335931</v>
+        <v>205430.854335931</v>
       </c>
       <c r="E8" s="11" t="n">
         <f aca="false">MAX(0,E6-'Your numbers'!$B$9)</f>
-        <v>337332.012318055</v>
+        <v>330212.618568055</v>
       </c>
       <c r="F8" s="11" t="n">
         <f aca="false">MAX(0,F6-'Your numbers'!$B$9)</f>
-        <v>329969.659557169</v>
+        <v>321947.318307169</v>
       </c>
       <c r="G8" s="11" t="n">
         <f aca="false">MAX(0,G6-'Your numbers'!$B$9)</f>
-        <v>316088.769207364</v>
+        <v>364099.926862789</v>
       </c>
       <c r="H8" s="11" t="n">
         <f aca="false">MAX(0,H6-'Your numbers'!$B$9)</f>
-        <v>447197.758851492</v>
+        <v>496151.297211341</v>
       </c>
       <c r="I8" s="11" t="n">
         <f aca="false">MAX(0,I6-'Your numbers'!$B$9)</f>
-        <v>585647.486330165</v>
+        <v>635530.442582843</v>
       </c>
       <c r="J8" s="11" t="n">
         <f aca="false">MAX(0,J6-'Your numbers'!$B$9)</f>
-        <v>731486.5874483</v>
+        <v>719075.961720472</v>
       </c>
       <c r="K8" s="11" t="n">
         <f aca="false">MAX(0,K6-'Your numbers'!$B$9)</f>
-        <v>748428.470548401</v>
+        <v>879166.335282246</v>
       </c>
       <c r="L8" s="11" t="n">
         <f aca="false">MAX(0,L6-'Your numbers'!$B$9)</f>
-        <v>912695.917051482</v>
+        <v>1047070.66564829</v>
       </c>
       <c r="M8" s="11" t="n">
         <f aca="false">MAX(0,M6-'Your numbers'!$B$9)</f>
-        <v>1084746.42040954</v>
+        <v>1222827.40169565</v>
       </c>
       <c r="N8" s="11" t="n">
         <f aca="false">MAX(0,N6-'Your numbers'!$B$9)</f>
-        <v>1264609.86275326</v>
+        <v>1406465.40590655</v>
       </c>
       <c r="O8" s="11" t="n">
         <f aca="false">MAX(0,O6-'Your numbers'!$B$9)</f>
-        <v>1330797.94885832</v>
+        <v>1477343.6700041</v>
       </c>
       <c r="P8" s="11" t="n">
         <f aca="false">MAX(0,P6-'Your numbers'!$B$9)</f>
-        <v>1394843.49387317</v>
+        <v>1546229.81094027</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -1470,63 +1470,63 @@
       </c>
       <c r="B9" s="11" t="n">
         <f aca="false">B8*'Your numbers'!$B$8</f>
-        <v>16414.607309104</v>
+        <v>15934.607309104</v>
       </c>
       <c r="C9" s="11" t="n">
         <f aca="false">C8*'Your numbers'!$B$8</f>
-        <v>15372.624221904</v>
+        <v>14868.624221904</v>
       </c>
       <c r="D9" s="11" t="n">
         <f aca="false">D8*'Your numbers'!$B$8</f>
-        <v>21121.8979335931</v>
+        <v>20543.0854335931</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">E8*'Your numbers'!$B$8</f>
-        <v>33733.2012318055</v>
+        <v>33021.2618568055</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">F8*'Your numbers'!$B$8</f>
-        <v>32996.9659557169</v>
+        <v>32194.7318307169</v>
       </c>
       <c r="G9" s="11" t="n">
         <f aca="false">G8*'Your numbers'!$B$8</f>
-        <v>31608.8769207364</v>
+        <v>36409.9926862789</v>
       </c>
       <c r="H9" s="11" t="n">
         <f aca="false">H8*'Your numbers'!$B$8</f>
-        <v>44719.7758851492</v>
+        <v>49615.1297211341</v>
       </c>
       <c r="I9" s="11" t="n">
         <f aca="false">I8*'Your numbers'!$B$8</f>
-        <v>58564.7486330165</v>
+        <v>63553.0442582843</v>
       </c>
       <c r="J9" s="11" t="n">
         <f aca="false">J8*'Your numbers'!$B$8</f>
-        <v>73148.65874483</v>
+        <v>71907.5961720472</v>
       </c>
       <c r="K9" s="11" t="n">
         <f aca="false">K8*'Your numbers'!$B$8</f>
-        <v>74842.8470548401</v>
+        <v>87916.6335282246</v>
       </c>
       <c r="L9" s="11" t="n">
         <f aca="false">L8*'Your numbers'!$B$8</f>
-        <v>91269.5917051482</v>
+        <v>104707.066564829</v>
       </c>
       <c r="M9" s="11" t="n">
         <f aca="false">M8*'Your numbers'!$B$8</f>
-        <v>108474.642040954</v>
+        <v>122282.740169565</v>
       </c>
       <c r="N9" s="11" t="n">
         <f aca="false">N8*'Your numbers'!$B$8</f>
-        <v>126460.986275326</v>
+        <v>140646.540590655</v>
       </c>
       <c r="O9" s="11" t="n">
         <f aca="false">O8*'Your numbers'!$B$8</f>
-        <v>133079.794885832</v>
+        <v>147734.36700041</v>
       </c>
       <c r="P9" s="11" t="n">
         <f aca="false">P8*'Your numbers'!$B$8</f>
-        <v>139484.349387317</v>
+        <v>154622.981094027</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
@@ -1537,63 +1537,63 @@
       </c>
       <c r="B10" s="10" t="n">
         <f aca="false">B7+B9</f>
-        <v>76414.607309104</v>
+        <v>75934.607309104</v>
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">C7+C9</f>
-        <v>75372.624221904</v>
+        <v>74868.624221904</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">D7+D9</f>
-        <v>87121.8979335931</v>
+        <v>86543.0854335931</v>
       </c>
       <c r="E10" s="10" t="n">
         <f aca="false">E7+E9</f>
-        <v>105733.201231806</v>
+        <v>105021.261856806</v>
       </c>
       <c r="F10" s="10" t="n">
         <f aca="false">F7+F9</f>
-        <v>104996.965955717</v>
+        <v>104194.731830717</v>
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">G7+G9</f>
-        <v>105588.876920736</v>
+        <v>110389.992686279</v>
       </c>
       <c r="H10" s="10" t="n">
         <f aca="false">H7+H9</f>
-        <v>120734.225885149</v>
+        <v>125629.579721134</v>
       </c>
       <c r="I10" s="10" t="n">
         <f aca="false">I7+I9</f>
-        <v>136669.596008017</v>
+        <v>141657.891633284</v>
       </c>
       <c r="J10" s="10" t="n">
         <f aca="false">J7+J9</f>
-        <v>153401.389422643</v>
+        <v>152160.32684986</v>
       </c>
       <c r="K10" s="10" t="n">
         <f aca="false">K7+K9</f>
-        <v>157302.527826293</v>
+        <v>170376.314299677</v>
       </c>
       <c r="L10" s="10" t="n">
         <f aca="false">L7+L9</f>
-        <v>175996.913697816</v>
+        <v>189434.388557496</v>
       </c>
       <c r="M10" s="10" t="n">
         <f aca="false">M7+M9</f>
-        <v>195531.96538842</v>
+        <v>209340.063517031</v>
       </c>
       <c r="N10" s="10" t="n">
         <f aca="false">N7+N9</f>
-        <v>215912.386014847</v>
+        <v>230097.940330176</v>
       </c>
       <c r="O10" s="10" t="n">
         <f aca="false">O7+O9</f>
-        <v>224991.10811819</v>
+        <v>239645.680232768</v>
       </c>
       <c r="P10" s="10" t="n">
         <f aca="false">P7+P9</f>
-        <v>233923.223733565</v>
+        <v>249061.855440275</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -1604,63 +1604,63 @@
       </c>
       <c r="B11" s="10" t="n">
         <f aca="false">B10</f>
-        <v>76414.607309104</v>
+        <v>75934.607309104</v>
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">B11+C10</f>
-        <v>151787.231531008</v>
+        <v>150803.231531008</v>
       </c>
       <c r="D11" s="10" t="n">
         <f aca="false">C11+D10</f>
-        <v>238909.129464601</v>
+        <v>237346.316964601</v>
       </c>
       <c r="E11" s="10" t="n">
         <f aca="false">D11+E10</f>
-        <v>344642.330696407</v>
+        <v>342367.578821407</v>
       </c>
       <c r="F11" s="10" t="n">
         <f aca="false">E11+F10</f>
-        <v>449639.296652124</v>
+        <v>446562.310652124</v>
       </c>
       <c r="G11" s="10" t="n">
         <f aca="false">F11+G10</f>
-        <v>555228.17357286</v>
+        <v>556952.303338402</v>
       </c>
       <c r="H11" s="10" t="n">
         <f aca="false">G11+H10</f>
-        <v>675962.399458009</v>
+        <v>682581.883059537</v>
       </c>
       <c r="I11" s="10" t="n">
         <f aca="false">H11+I10</f>
-        <v>812631.995466026</v>
+        <v>824239.774692821</v>
       </c>
       <c r="J11" s="10" t="n">
         <f aca="false">I11+J10</f>
-        <v>966033.384888668</v>
+        <v>976400.101542681</v>
       </c>
       <c r="K11" s="10" t="n">
         <f aca="false">J11+K10</f>
-        <v>1123335.91271496</v>
+        <v>1146776.41584236</v>
       </c>
       <c r="L11" s="10" t="n">
         <f aca="false">K11+L10</f>
-        <v>1299332.82641278</v>
+        <v>1336210.80439985</v>
       </c>
       <c r="M11" s="10" t="n">
         <f aca="false">L11+M10</f>
-        <v>1494864.7918012</v>
+        <v>1545550.86791688</v>
       </c>
       <c r="N11" s="10" t="n">
         <f aca="false">M11+N10</f>
-        <v>1710777.17781604</v>
+        <v>1775648.80824706</v>
       </c>
       <c r="O11" s="10" t="n">
         <f aca="false">N11+O10</f>
-        <v>1935768.28593423</v>
+        <v>2015294.48847983</v>
       </c>
       <c r="P11" s="10" t="n">
         <f aca="false">O11+P10</f>
-        <v>2169691.5096678</v>
+        <v>2264356.3439201</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
@@ -1671,63 +1671,63 @@
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">B10/1107883.476</f>
-        <v>0.0689735057562173</v>
+        <v>0.0685402471957295</v>
       </c>
       <c r="C12" s="12" t="n">
         <f aca="false">C10/1130224.27392</f>
-        <v>0.0666882015907217</v>
+        <v>0.0662422723962867</v>
       </c>
       <c r="D12" s="12" t="n">
         <f aca="false">D10/1470581.13731659</f>
-        <v>0.0592431765394236</v>
+        <v>0.0588495821396912</v>
       </c>
       <c r="E12" s="12" t="n">
         <f aca="false">E10/2128361.5241759</f>
-        <v>0.0496782149229771</v>
+        <v>0.0493437137741294</v>
       </c>
       <c r="F12" s="12" t="n">
         <f aca="false">F10/2531696.60117519</f>
-        <v>0.0414729655626896</v>
+        <v>0.0411560894707331</v>
       </c>
       <c r="G12" s="12" t="n">
         <f aca="false">G10/2960567.60023987</f>
-        <v>0.0356650788558861</v>
+        <v>0.0372867664556401</v>
       </c>
       <c r="H12" s="12" t="n">
         <f aca="false">H10/3415973.30476096</f>
-        <v>0.0353440191458399</v>
+        <v>0.0367770964562398</v>
       </c>
       <c r="I12" s="12" t="n">
         <f aca="false">I10/3898958.3702101</f>
-        <v>0.0350528482305011</v>
+        <v>0.0363322400966417</v>
       </c>
       <c r="J12" s="12" t="n">
         <f aca="false">J10/4410614.70976327</f>
-        <v>0.0347800475709374</v>
+        <v>0.0344986667080758</v>
       </c>
       <c r="K12" s="12" t="n">
         <f aca="false">K10/4952082.94628947</f>
-        <v>0.0317649218586206</v>
+        <v>0.0344049799140254</v>
       </c>
       <c r="L12" s="12" t="n">
         <f aca="false">L10/5524553.93215493</f>
-        <v>0.031857217045787</v>
+        <v>0.03428953556864</v>
       </c>
       <c r="M12" s="12" t="n">
         <f aca="false">M10/6129270.33838766</f>
-        <v>0.0319013446288707</v>
+        <v>0.034154157340056</v>
       </c>
       <c r="N12" s="12" t="n">
         <f aca="false">N10/6767528.314843</f>
-        <v>0.031904171799517</v>
+        <v>0.0340002922227174</v>
       </c>
       <c r="O12" s="12" t="n">
         <f aca="false">O10/7045784.99129078</f>
-        <v>0.0319327240891255</v>
+        <v>0.0340126303213895</v>
       </c>
       <c r="P12" s="12" t="n">
         <f aca="false">P10/7328447.27269707</f>
-        <v>0.0319198890336663</v>
+        <v>0.0339856242628888</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="6" t="s">
@@ -1761,49 +1761,49 @@
         <v>30</v>
       </c>
       <c r="B14" s="11" t="n">
-        <v>691314.397345807</v>
+        <v>737130.151233105</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>752384.283227823</v>
+        <v>793606.669249441</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>925823.920331045</v>
+        <v>973791.845154872</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1742417.68455785</v>
+        <v>1704841.10205784</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>1826323.55921217</v>
+        <v>1781926.25021217</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>1879798.57190215</v>
+        <v>2078739.72158601</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>2566573.43382394</v>
+        <v>2788865.52166945</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>3338763.68812422</v>
+        <v>3584726.63004211</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>4199351.48996621</v>
+        <v>4191175.85367095</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>4551505.48237858</v>
+        <v>5168218.95382355</v>
       </c>
       <c r="L14" s="11" t="n">
-        <v>7514344.27315891</v>
+        <v>8245690.54355842</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>8966057.46435439</v>
+        <v>9739722.17619467</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>10536753.2656805</v>
+        <v>11353079.965143</v>
       </c>
       <c r="O14" s="11" t="n">
-        <v>11512931.8634761</v>
+        <v>12401842.2665323</v>
       </c>
       <c r="P14" s="11" t="n">
-        <v>12490190.7073309</v>
+        <v>13454921.9845546</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -1814,63 +1814,63 @@
       </c>
       <c r="B15" s="11" t="n">
         <f aca="false">MAX(0,B14-'Your numbers'!$B$11)</f>
-        <v>521314.397345807</v>
+        <v>567130.151233105</v>
       </c>
       <c r="C15" s="11" t="n">
         <f aca="false">MAX(0,C14-'Your numbers'!$B$11)</f>
-        <v>582384.283227823</v>
+        <v>623606.669249441</v>
       </c>
       <c r="D15" s="11" t="n">
         <f aca="false">MAX(0,D14-'Your numbers'!$B$11)</f>
-        <v>755823.920331045</v>
+        <v>803791.845154872</v>
       </c>
       <c r="E15" s="11" t="n">
         <f aca="false">MAX(0,E14-'Your numbers'!$B$11)</f>
-        <v>1572417.68455785</v>
+        <v>1534841.10205784</v>
       </c>
       <c r="F15" s="11" t="n">
         <f aca="false">MAX(0,F14-'Your numbers'!$B$11)</f>
-        <v>1656323.55921217</v>
+        <v>1611926.25021217</v>
       </c>
       <c r="G15" s="11" t="n">
         <f aca="false">MAX(0,G14-'Your numbers'!$B$11)</f>
-        <v>1709798.57190215</v>
+        <v>1908739.72158601</v>
       </c>
       <c r="H15" s="11" t="n">
         <f aca="false">MAX(0,H14-'Your numbers'!$B$11)</f>
-        <v>2396573.43382394</v>
+        <v>2618865.52166945</v>
       </c>
       <c r="I15" s="11" t="n">
         <f aca="false">MAX(0,I14-'Your numbers'!$B$11)</f>
-        <v>3168763.68812422</v>
+        <v>3414726.63004211</v>
       </c>
       <c r="J15" s="11" t="n">
         <f aca="false">MAX(0,J14-'Your numbers'!$B$11)</f>
-        <v>4029351.48996621</v>
+        <v>4021175.85367095</v>
       </c>
       <c r="K15" s="11" t="n">
         <f aca="false">MAX(0,K14-'Your numbers'!$B$11)</f>
-        <v>4381505.48237858</v>
+        <v>4998218.95382355</v>
       </c>
       <c r="L15" s="11" t="n">
         <f aca="false">MAX(0,L14-'Your numbers'!$B$11)</f>
-        <v>7344344.27315891</v>
+        <v>8075690.54355842</v>
       </c>
       <c r="M15" s="11" t="n">
         <f aca="false">MAX(0,M14-'Your numbers'!$B$11)</f>
-        <v>8796057.46435439</v>
+        <v>9569722.17619467</v>
       </c>
       <c r="N15" s="11" t="n">
         <f aca="false">MAX(0,N14-'Your numbers'!$B$11)</f>
-        <v>10366753.2656805</v>
+        <v>11183079.965143</v>
       </c>
       <c r="O15" s="11" t="n">
         <f aca="false">MAX(0,O14-'Your numbers'!$B$11)</f>
-        <v>11342931.8634761</v>
+        <v>12231842.2665323</v>
       </c>
       <c r="P15" s="11" t="n">
         <f aca="false">MAX(0,P14-'Your numbers'!$B$11)</f>
-        <v>12320190.7073309</v>
+        <v>13284921.9845546</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -1881,63 +1881,63 @@
       </c>
       <c r="B16" s="10" t="n">
         <f aca="false">B15*'Your numbers'!$B$10</f>
-        <v>78197.1596018711</v>
+        <v>85069.5226849658</v>
       </c>
       <c r="C16" s="10" t="n">
         <f aca="false">C15*'Your numbers'!$B$10</f>
-        <v>87357.6424841734</v>
+        <v>93541.0003874162</v>
       </c>
       <c r="D16" s="10" t="n">
         <f aca="false">D15*'Your numbers'!$B$10</f>
-        <v>113373.588049657</v>
+        <v>120568.776773231</v>
       </c>
       <c r="E16" s="10" t="n">
         <f aca="false">E15*'Your numbers'!$B$10</f>
-        <v>235862.652683678</v>
+        <v>230226.165308676</v>
       </c>
       <c r="F16" s="10" t="n">
         <f aca="false">F15*'Your numbers'!$B$10</f>
-        <v>248448.533881826</v>
+        <v>241788.937531825</v>
       </c>
       <c r="G16" s="10" t="n">
         <f aca="false">G15*'Your numbers'!$B$10</f>
-        <v>256469.785785322</v>
+        <v>286310.958237902</v>
       </c>
       <c r="H16" s="10" t="n">
         <f aca="false">H15*'Your numbers'!$B$10</f>
-        <v>359486.015073591</v>
+        <v>392829.828250418</v>
       </c>
       <c r="I16" s="10" t="n">
         <f aca="false">I15*'Your numbers'!$B$10</f>
-        <v>475314.553218633</v>
+        <v>512208.994506317</v>
       </c>
       <c r="J16" s="10" t="n">
         <f aca="false">J15*'Your numbers'!$B$10</f>
-        <v>604402.723494932</v>
+        <v>603176.378050642</v>
       </c>
       <c r="K16" s="10" t="n">
         <f aca="false">K15*'Your numbers'!$B$10</f>
-        <v>657225.822356787</v>
+        <v>749732.843073533</v>
       </c>
       <c r="L16" s="10" t="n">
         <f aca="false">L15*'Your numbers'!$B$10</f>
-        <v>1101651.64097384</v>
+        <v>1211353.58153376</v>
       </c>
       <c r="M16" s="10" t="n">
         <f aca="false">M15*'Your numbers'!$B$10</f>
-        <v>1319408.61965316</v>
+        <v>1435458.3264292</v>
       </c>
       <c r="N16" s="10" t="n">
         <f aca="false">N15*'Your numbers'!$B$10</f>
-        <v>1555012.98985207</v>
+        <v>1677461.99477145</v>
       </c>
       <c r="O16" s="10" t="n">
         <f aca="false">O15*'Your numbers'!$B$10</f>
-        <v>1701439.77952141</v>
+        <v>1834776.33997984</v>
       </c>
       <c r="P16" s="10" t="n">
         <f aca="false">P15*'Your numbers'!$B$10</f>
-        <v>1848028.60609964</v>
+        <v>1992738.29768319</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="6" t="s">
@@ -1950,63 +1950,63 @@
       </c>
       <c r="B17" s="10" t="n">
         <f aca="false">B11+B16</f>
-        <v>154611.766910975</v>
+        <v>161004.12999407</v>
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">C11+C16</f>
-        <v>239144.874015181</v>
+        <v>244344.231918424</v>
       </c>
       <c r="D17" s="10" t="n">
         <f aca="false">D11+D16</f>
-        <v>352282.717514258</v>
+        <v>357915.093737832</v>
       </c>
       <c r="E17" s="10" t="n">
         <f aca="false">E11+E16</f>
-        <v>580504.983380084</v>
+        <v>572593.744130083</v>
       </c>
       <c r="F17" s="10" t="n">
         <f aca="false">F11+F16</f>
-        <v>698087.830533949</v>
+        <v>688351.248183949</v>
       </c>
       <c r="G17" s="10" t="n">
         <f aca="false">G11+G16</f>
-        <v>811697.959358183</v>
+        <v>843263.261576304</v>
       </c>
       <c r="H17" s="10" t="n">
         <f aca="false">H11+H16</f>
-        <v>1035448.4145316</v>
+        <v>1075411.71130995</v>
       </c>
       <c r="I17" s="10" t="n">
         <f aca="false">I11+I16</f>
-        <v>1287946.54868466</v>
+        <v>1336448.76919914</v>
       </c>
       <c r="J17" s="10" t="n">
         <f aca="false">J11+J16</f>
-        <v>1570436.1083836</v>
+        <v>1579576.47959332</v>
       </c>
       <c r="K17" s="10" t="n">
         <f aca="false">K11+K16</f>
-        <v>1780561.73507175</v>
+        <v>1896509.25891589</v>
       </c>
       <c r="L17" s="10" t="n">
         <f aca="false">L11+L16</f>
-        <v>2400984.46738661</v>
+        <v>2547564.38593362</v>
       </c>
       <c r="M17" s="10" t="n">
         <f aca="false">M11+M16</f>
-        <v>2814273.41145435</v>
+        <v>2981009.19434608</v>
       </c>
       <c r="N17" s="10" t="n">
         <f aca="false">N11+N16</f>
-        <v>3265790.16766812</v>
+        <v>3453110.80301851</v>
       </c>
       <c r="O17" s="10" t="n">
         <f aca="false">O11+O16</f>
-        <v>3637208.06545565</v>
+        <v>3850070.82845967</v>
       </c>
       <c r="P17" s="10" t="n">
         <f aca="false">P11+P16</f>
-        <v>4017720.11576743</v>
+        <v>4257094.64160329</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="6" t="s">
@@ -2322,34 +2322,34 @@
         <v>19</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H9" s="17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>28</v>
       </c>
       <c r="K9" s="17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N9" s="17" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O9" s="17" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P9" s="17" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
@@ -2359,49 +2359,49 @@
         <v>42</v>
       </c>
       <c r="B10" s="10" t="n">
-        <v>314146.07309104</v>
+        <v>309346.07309104</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>303726.24221904</v>
+        <v>298686.24221904</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>361218.979335931</v>
+        <v>355430.854335931</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>487332.012318055</v>
+        <v>480212.618568055</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>479969.659557169</v>
+        <v>471947.318307169</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>466088.769207364</v>
+        <v>514099.926862789</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>597197.758851492</v>
+        <v>646151.297211341</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>735647.486330165</v>
+        <v>785530.442582843</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>881486.5874483</v>
+        <v>869075.961720472</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>898428.470548401</v>
+        <v>1029166.33528225</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>1062695.91705148</v>
+        <v>1197070.66564829</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>1234746.42040954</v>
+        <v>1372827.40169565</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>1414609.86275326</v>
+        <v>1556465.40590655</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>1480797.94885832</v>
+        <v>1627343.6700041</v>
       </c>
       <c r="P10" s="10" t="n">
-        <v>1544843.49387317</v>
+        <v>1696229.81094027</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="6" t="s">
@@ -2413,49 +2413,49 @@
         <v>44</v>
       </c>
       <c r="B11" s="11" t="n">
-        <v>62958.4292364159</v>
+        <v>61038.4292364159</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>124448.926124032</v>
+        <v>120512.926124032</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>195086.517858404</v>
+        <v>188835.267858404</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>302319.322785626</v>
+        <v>293220.315285626</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>420457.186608494</v>
+        <v>408149.242608494</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>533042.694291439</v>
+        <v>539939.213353609</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>698071.797832036</v>
+        <v>724549.732238146</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>918480.792364102</v>
+        <v>964911.909271283</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>1197225.42734342</v>
+        <v>1238692.29395947</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>1482746.81556278</v>
+        <v>1576508.82807237</v>
       </c>
       <c r="L11" s="11" t="n">
-        <v>1833975.18238338</v>
+        <v>1981487.09433169</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>2254023.75054719</v>
+        <v>2456768.05500994</v>
       </c>
       <c r="N11" s="11" t="n">
-        <v>2746017.69564849</v>
+        <v>3005504.21737256</v>
       </c>
       <c r="O11" s="11" t="n">
-        <v>3278336.87519182</v>
+        <v>3596441.6853742</v>
       </c>
       <c r="P11" s="11" t="n">
-        <v>3836274.27274109</v>
+        <v>4214933.60975031</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
@@ -2465,49 +2465,49 @@
         <v>30</v>
       </c>
       <c r="B12" s="10" t="n">
-        <v>691314.397345807</v>
+        <v>737130.151233105</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>752384.283227823</v>
+        <v>793606.669249441</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>925823.920331045</v>
+        <v>973791.845154872</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1742417.68455785</v>
+        <v>1704841.10205784</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1826323.55921217</v>
+        <v>1781926.25021217</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>1879798.57190215</v>
+        <v>2078739.72158601</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>2566573.43382394</v>
+        <v>2788865.52166945</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>3338763.68812422</v>
+        <v>3584726.63004211</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>4199351.48996621</v>
+        <v>4191175.85367095</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>4551505.48237858</v>
+        <v>5168218.95382355</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>7514344.27315891</v>
+        <v>8245690.54355842</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>8966057.46435439</v>
+        <v>9739722.17619467</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>10536753.2656805</v>
+        <v>11353079.965143</v>
       </c>
       <c r="O12" s="10" t="n">
-        <v>11512931.8634761</v>
+        <v>12401842.2665323</v>
       </c>
       <c r="P12" s="10" t="n">
-        <v>12490190.7073309</v>
+        <v>13454921.9845546</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="6" t="s">
@@ -2755,63 +2755,63 @@
       </c>
       <c r="B9" s="10" t="n">
         <f aca="false">'Year by year'!B16</f>
-        <v>78197.1596018711</v>
+        <v>85069.5226849658</v>
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">'Year by year'!C16</f>
-        <v>87357.6424841734</v>
+        <v>93541.0003874162</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">'Year by year'!D16</f>
-        <v>113373.588049657</v>
+        <v>120568.776773231</v>
       </c>
       <c r="E9" s="10" t="n">
         <f aca="false">'Year by year'!E16</f>
-        <v>235862.652683678</v>
+        <v>230226.165308676</v>
       </c>
       <c r="F9" s="10" t="n">
         <f aca="false">'Year by year'!F16</f>
-        <v>248448.533881826</v>
+        <v>241788.937531825</v>
       </c>
       <c r="G9" s="10" t="n">
         <f aca="false">'Year by year'!G16</f>
-        <v>256469.785785322</v>
+        <v>286310.958237902</v>
       </c>
       <c r="H9" s="10" t="n">
         <f aca="false">'Year by year'!H16</f>
-        <v>359486.015073591</v>
+        <v>392829.828250418</v>
       </c>
       <c r="I9" s="10" t="n">
         <f aca="false">'Year by year'!I16</f>
-        <v>475314.553218633</v>
+        <v>512208.994506317</v>
       </c>
       <c r="J9" s="10" t="n">
         <f aca="false">'Year by year'!J16</f>
-        <v>604402.723494932</v>
+        <v>603176.378050642</v>
       </c>
       <c r="K9" s="10" t="n">
         <f aca="false">'Year by year'!K16</f>
-        <v>657225.822356787</v>
+        <v>749732.843073533</v>
       </c>
       <c r="L9" s="10" t="n">
         <f aca="false">'Year by year'!L16</f>
-        <v>1101651.64097384</v>
+        <v>1211353.58153376</v>
       </c>
       <c r="M9" s="10" t="n">
         <f aca="false">'Year by year'!M16</f>
-        <v>1319408.61965316</v>
+        <v>1435458.3264292</v>
       </c>
       <c r="N9" s="10" t="n">
         <f aca="false">'Year by year'!N16</f>
-        <v>1555012.98985207</v>
+        <v>1677461.99477145</v>
       </c>
       <c r="O9" s="10" t="n">
         <f aca="false">'Year by year'!O16</f>
-        <v>1701439.77952141</v>
+        <v>1834776.33997984</v>
       </c>
       <c r="P9" s="10" t="n">
         <f aca="false">'Year by year'!P16</f>
-        <v>1848028.60609964</v>
+        <v>1992738.29768319</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="6" t="s">
@@ -2824,63 +2824,63 @@
       </c>
       <c r="B10" s="10" t="n">
         <f aca="false">B9*(1-$B$4)</f>
-        <v>62557.7276814969</v>
+        <v>68055.6181479726</v>
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">C9*(1-$B$4)</f>
-        <v>69886.1139873388</v>
+        <v>74832.8003099329</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">D9*(1-$B$4)</f>
-        <v>90698.8704397254</v>
+        <v>96455.0214185846</v>
       </c>
       <c r="E10" s="10" t="n">
         <f aca="false">E9*(1-$B$4)</f>
-        <v>188690.122146942</v>
+        <v>184180.932246941</v>
       </c>
       <c r="F10" s="10" t="n">
         <f aca="false">F9*(1-$B$4)</f>
-        <v>198758.82710546</v>
+        <v>193431.15002546</v>
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">G9*(1-$B$4)</f>
-        <v>205175.828628258</v>
+        <v>229048.766590321</v>
       </c>
       <c r="H10" s="10" t="n">
         <f aca="false">H9*(1-$B$4)</f>
-        <v>287588.812058873</v>
+        <v>314263.862600334</v>
       </c>
       <c r="I10" s="10" t="n">
         <f aca="false">I9*(1-$B$4)</f>
-        <v>380251.642574906</v>
+        <v>409767.195605053</v>
       </c>
       <c r="J10" s="10" t="n">
         <f aca="false">J9*(1-$B$4)</f>
-        <v>483522.178795945</v>
+        <v>482541.102440514</v>
       </c>
       <c r="K10" s="10" t="n">
         <f aca="false">K9*(1-$B$4)</f>
-        <v>525780.65788543</v>
+        <v>599786.274458826</v>
       </c>
       <c r="L10" s="10" t="n">
         <f aca="false">L9*(1-$B$4)</f>
-        <v>881321.312779069</v>
+        <v>969082.86522701</v>
       </c>
       <c r="M10" s="10" t="n">
         <f aca="false">M9*(1-$B$4)</f>
-        <v>1055526.89572253</v>
+        <v>1148366.66114336</v>
       </c>
       <c r="N10" s="10" t="n">
         <f aca="false">N9*(1-$B$4)</f>
-        <v>1244010.39188166</v>
+        <v>1341969.59581716</v>
       </c>
       <c r="O10" s="10" t="n">
         <f aca="false">O9*(1-$B$4)</f>
-        <v>1361151.82361713</v>
+        <v>1467821.07198388</v>
       </c>
       <c r="P10" s="10" t="n">
         <f aca="false">P9*(1-$B$4)</f>
-        <v>1478422.88487971</v>
+        <v>1594190.63814655</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -2891,63 +2891,63 @@
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">B10</f>
-        <v>62557.7276814969</v>
+        <v>68055.6181479726</v>
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">C10</f>
-        <v>69886.1139873388</v>
+        <v>74832.8003099329</v>
       </c>
       <c r="D11" s="11" t="n">
         <f aca="false">D10</f>
-        <v>90698.8704397254</v>
+        <v>96455.0214185846</v>
       </c>
       <c r="E11" s="11" t="n">
         <f aca="false">E10</f>
-        <v>188690.122146942</v>
+        <v>184180.932246941</v>
       </c>
       <c r="F11" s="11" t="n">
         <f aca="false">F10</f>
-        <v>198758.82710546</v>
+        <v>193431.15002546</v>
       </c>
       <c r="G11" s="11" t="n">
         <f aca="false">G10</f>
-        <v>205175.828628258</v>
+        <v>229048.766590321</v>
       </c>
       <c r="H11" s="11" t="n">
         <f aca="false">H10</f>
-        <v>287588.812058873</v>
+        <v>314263.862600334</v>
       </c>
       <c r="I11" s="11" t="n">
         <f aca="false">I10</f>
-        <v>380251.642574906</v>
+        <v>409767.195605053</v>
       </c>
       <c r="J11" s="11" t="n">
         <f aca="false">J10</f>
-        <v>483522.178795945</v>
+        <v>482541.102440514</v>
       </c>
       <c r="K11" s="11" t="n">
         <f aca="false">K10</f>
-        <v>525780.65788543</v>
+        <v>599786.274458826</v>
       </c>
       <c r="L11" s="11" t="n">
         <f aca="false">L10</f>
-        <v>881321.312779069</v>
+        <v>969082.86522701</v>
       </c>
       <c r="M11" s="11" t="n">
         <f aca="false">M10</f>
-        <v>1055526.89572253</v>
+        <v>1148366.66114336</v>
       </c>
       <c r="N11" s="11" t="n">
         <f aca="false">N10</f>
-        <v>1244010.39188166</v>
+        <v>1341969.59581716</v>
       </c>
       <c r="O11" s="11" t="n">
         <f aca="false">O10</f>
-        <v>1361151.82361713</v>
+        <v>1467821.07198388</v>
       </c>
       <c r="P11" s="11" t="n">
         <f aca="false">P10</f>
-        <v>1478422.88487971</v>
+        <v>1594190.63814655</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
@@ -2958,63 +2958,63 @@
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,36,-B10))</f>
-        <v>1982.04821671552</v>
+        <v>2156.24066900944</v>
       </c>
       <c r="C12" s="11" t="n">
         <f aca="false">IF(C10=0,0,PMT($B$5/12,36,-C10))</f>
-        <v>2214.2371971537</v>
+        <v>2370.9655689748</v>
       </c>
       <c r="D12" s="11" t="n">
         <f aca="false">IF(D10=0,0,PMT($B$5/12,36,-D10))</f>
-        <v>2873.6583164983</v>
+        <v>3056.03336760119</v>
       </c>
       <c r="E12" s="11" t="n">
         <f aca="false">IF(E10=0,0,PMT($B$5/12,36,-E10))</f>
-        <v>5978.36484754222</v>
+        <v>5835.49789678543</v>
       </c>
       <c r="F12" s="11" t="n">
         <f aca="false">IF(F10=0,0,PMT($B$5/12,36,-F10))</f>
-        <v>6297.37673379986</v>
+        <v>6128.57723856542</v>
       </c>
       <c r="G12" s="11" t="n">
         <f aca="false">IF(G10=0,0,PMT($B$5/12,36,-G10))</f>
-        <v>6500.68984788351</v>
+        <v>7257.068250187</v>
       </c>
       <c r="H12" s="11" t="n">
         <f aca="false">IF(H10=0,0,PMT($B$5/12,36,-H10))</f>
-        <v>9111.82220349766</v>
+        <v>9956.98135994409</v>
       </c>
       <c r="I12" s="11" t="n">
         <f aca="false">IF(I10=0,0,PMT($B$5/12,36,-I10))</f>
-        <v>12047.7056632551</v>
+        <v>12982.8619008126</v>
       </c>
       <c r="J12" s="11" t="n">
         <f aca="false">IF(J10=0,0,PMT($B$5/12,36,-J10))</f>
-        <v>15319.6784433135</v>
+        <v>15288.594503522</v>
       </c>
       <c r="K12" s="11" t="n">
         <f aca="false">IF(K10=0,0,PMT($B$5/12,36,-K10))</f>
-        <v>16658.5752706866</v>
+        <v>19003.3327577719</v>
       </c>
       <c r="L12" s="11" t="n">
         <f aca="false">IF(L10=0,0,PMT($B$5/12,36,-L10))</f>
-        <v>27923.3501773084</v>
+        <v>30703.9439580041</v>
       </c>
       <c r="M12" s="11" t="n">
         <f aca="false">IF(M10=0,0,PMT($B$5/12,36,-M10))</f>
-        <v>33442.7940224066</v>
+        <v>36384.2834004979</v>
       </c>
       <c r="N12" s="11" t="n">
         <f aca="false">IF(N10=0,0,PMT($B$5/12,36,-N10))</f>
-        <v>39414.612233972</v>
+        <v>42518.3033792094</v>
       </c>
       <c r="O12" s="11" t="n">
         <f aca="false">IF(O10=0,0,PMT($B$5/12,36,-O10))</f>
-        <v>43126.0636322214</v>
+        <v>46505.7195330898</v>
       </c>
       <c r="P12" s="11" t="n">
         <f aca="false">IF(P10=0,0,PMT($B$5/12,36,-P10))</f>
-        <v>46841.6221485288</v>
+        <v>50509.5505950983</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
@@ -3025,63 +3025,63 @@
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,60,-B10))</f>
-        <v>1291.0183837808</v>
+        <v>1404.47962873476</v>
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">IF(C10=0,0,PMT($B$5/12,60,-C10))</f>
-        <v>1442.25599734086</v>
+        <v>1544.3419141085</v>
       </c>
       <c r="D13" s="10" t="n">
         <f aca="false">IF(D10=0,0,PMT($B$5/12,60,-D10))</f>
-        <v>1871.77369552175</v>
+        <v>1990.56472276878</v>
       </c>
       <c r="E13" s="10" t="n">
         <f aca="false">IF(E10=0,0,PMT($B$5/12,60,-E10))</f>
-        <v>3894.04196024849</v>
+        <v>3800.98475896235</v>
       </c>
       <c r="F13" s="10" t="n">
         <f aca="false">IF(F10=0,0,PMT($B$5/12,60,-F10))</f>
-        <v>4101.83216753501</v>
+        <v>3991.88365584759</v>
       </c>
       <c r="G13" s="10" t="n">
         <f aca="false">IF(G10=0,0,PMT($B$5/12,60,-G10))</f>
-        <v>4234.26132124181</v>
+        <v>4726.93269736339</v>
       </c>
       <c r="H13" s="10" t="n">
         <f aca="false">IF(H10=0,0,PMT($B$5/12,60,-H10))</f>
-        <v>5935.03723837308</v>
+        <v>6485.53646386676</v>
       </c>
       <c r="I13" s="10" t="n">
         <f aca="false">IF(I10=0,0,PMT($B$5/12,60,-I10))</f>
-        <v>7847.34163501675</v>
+        <v>8456.4609713741</v>
       </c>
       <c r="J13" s="10" t="n">
         <f aca="false">IF(J10=0,0,PMT($B$5/12,60,-J10))</f>
-        <v>9978.55972278141</v>
+        <v>9958.3130217311</v>
       </c>
       <c r="K13" s="10" t="n">
         <f aca="false">IF(K10=0,0,PMT($B$5/12,60,-K10))</f>
-        <v>10850.6577895927</v>
+        <v>12377.9289204389</v>
       </c>
       <c r="L13" s="10" t="n">
         <f aca="false">IF(L10=0,0,PMT($B$5/12,60,-L10))</f>
-        <v>18188.0330214127</v>
+        <v>19999.1886020037</v>
       </c>
       <c r="M13" s="10" t="n">
         <f aca="false">IF(M10=0,0,PMT($B$5/12,60,-M10))</f>
-        <v>21783.154175466</v>
+        <v>23699.110018914</v>
       </c>
       <c r="N13" s="10" t="n">
         <f aca="false">IF(N10=0,0,PMT($B$5/12,60,-N10))</f>
-        <v>25672.9319471208</v>
+        <v>27694.5388345248</v>
       </c>
       <c r="O13" s="10" t="n">
         <f aca="false">IF(O10=0,0,PMT($B$5/12,60,-O10))</f>
-        <v>28090.4069334705</v>
+        <v>30291.76503469</v>
       </c>
       <c r="P13" s="10" t="n">
         <f aca="false">IF(P10=0,0,PMT($B$5/12,60,-P10))</f>
-        <v>30510.5571145368</v>
+        <v>32899.683178665</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="6" t="s">
@@ -3094,63 +3094,63 @@
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,84,-B10))</f>
-        <v>998.577247232027</v>
+        <v>1086.33728154063</v>
       </c>
       <c r="C14" s="11" t="n">
         <f aca="false">IF(C10=0,0,PMT($B$5/12,84,-C10))</f>
-        <v>1115.55655730542</v>
+        <v>1194.51799970444</v>
       </c>
       <c r="D14" s="11" t="n">
         <f aca="false">IF(D10=0,0,PMT($B$5/12,84,-D10))</f>
-        <v>1447.78002218811</v>
+        <v>1539.66253794038</v>
       </c>
       <c r="E14" s="11" t="n">
         <f aca="false">IF(E10=0,0,PMT($B$5/12,84,-E10))</f>
-        <v>3011.96462430171</v>
+        <v>2939.98671518527</v>
       </c>
       <c r="F14" s="11" t="n">
         <f aca="false">IF(F10=0,0,PMT($B$5/12,84,-F10))</f>
-        <v>3172.6862498035</v>
+        <v>3087.64324536808</v>
       </c>
       <c r="G14" s="11" t="n">
         <f aca="false">IF(G10=0,0,PMT($B$5/12,84,-G10))</f>
-        <v>3275.1175872834</v>
+        <v>3656.18917599056</v>
       </c>
       <c r="H14" s="11" t="n">
         <f aca="false">IF(H10=0,0,PMT($B$5/12,84,-H10))</f>
-        <v>4590.63420178254</v>
+        <v>5016.43449099839</v>
       </c>
       <c r="I14" s="11" t="n">
         <f aca="false">IF(I10=0,0,PMT($B$5/12,84,-I10))</f>
-        <v>6069.76392159168</v>
+        <v>6540.90570994811</v>
       </c>
       <c r="J14" s="11" t="n">
         <f aca="false">IF(J10=0,0,PMT($B$5/12,84,-J10))</f>
-        <v>7718.21906217508</v>
+        <v>7702.55863839309</v>
       </c>
       <c r="K14" s="11" t="n">
         <f aca="false">IF(K10=0,0,PMT($B$5/12,84,-K10))</f>
-        <v>8392.76970979828</v>
+        <v>9574.08379546685</v>
       </c>
       <c r="L14" s="11" t="n">
         <f aca="false">IF(L10=0,0,PMT($B$5/12,84,-L10))</f>
-        <v>14068.0846804821</v>
+        <v>15468.9777868057</v>
       </c>
       <c r="M14" s="11" t="n">
         <f aca="false">IF(M10=0,0,PMT($B$5/12,84,-M10))</f>
-        <v>16848.8399590915</v>
+        <v>18330.7940009584</v>
       </c>
       <c r="N14" s="11" t="n">
         <f aca="false">IF(N10=0,0,PMT($B$5/12,84,-N10))</f>
-        <v>19857.5063176511</v>
+        <v>21421.1793574551</v>
       </c>
       <c r="O14" s="11" t="n">
         <f aca="false">IF(O10=0,0,PMT($B$5/12,84,-O10))</f>
-        <v>21727.3755212575</v>
+        <v>23430.0825783407</v>
       </c>
       <c r="P14" s="11" t="n">
         <f aca="false">IF(P10=0,0,PMT($B$5/12,84,-P10))</f>
-        <v>23599.3139351938</v>
+        <v>25447.2558068043</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -3182,49 +3182,49 @@
         <v>61</v>
       </c>
       <c r="B16" s="11" t="n">
-        <v>314146.07309104</v>
+        <v>309346.07309104</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>303726.24221904</v>
+        <v>298686.24221904</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>361218.979335931</v>
+        <v>355430.854335931</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>487332.012318055</v>
+        <v>480212.618568055</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>479969.659557169</v>
+        <v>471947.318307169</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>466088.769207364</v>
+        <v>514099.926862789</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>597197.758851492</v>
+        <v>646151.297211341</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>735647.486330165</v>
+        <v>785530.442582843</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>881486.5874483</v>
+        <v>869075.961720472</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>898428.470548401</v>
+        <v>1029166.33528225</v>
       </c>
       <c r="L16" s="11" t="n">
-        <v>1062695.91705148</v>
+        <v>1197070.66564829</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>1234746.42040954</v>
+        <v>1372827.40169565</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>1414609.86275326</v>
+        <v>1556465.40590655</v>
       </c>
       <c r="O16" s="11" t="n">
-        <v>1480797.94885832</v>
+        <v>1627343.6700041</v>
       </c>
       <c r="P16" s="11" t="n">
-        <v>1544843.49387317</v>
+        <v>1696229.81094027</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -3234,49 +3234,49 @@
         <v>44</v>
       </c>
       <c r="B17" s="11" t="n">
-        <v>62958.4292364159</v>
+        <v>61038.4292364159</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>124448.926124032</v>
+        <v>120512.926124032</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>195086.517858404</v>
+        <v>188835.267858404</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>302319.322785626</v>
+        <v>293220.315285626</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>420457.186608494</v>
+        <v>408149.242608494</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>533042.694291439</v>
+        <v>539939.213353609</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>698071.797832036</v>
+        <v>724549.732238146</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>918480.792364102</v>
+        <v>964911.909271283</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>1197225.42734342</v>
+        <v>1238692.29395947</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>1482746.81556278</v>
+        <v>1576508.82807237</v>
       </c>
       <c r="L17" s="11" t="n">
-        <v>1833975.18238338</v>
+        <v>1981487.09433169</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>2254023.75054719</v>
+        <v>2456768.05500994</v>
       </c>
       <c r="N17" s="11" t="n">
-        <v>2746017.69564849</v>
+        <v>3005504.21737256</v>
       </c>
       <c r="O17" s="11" t="n">
-        <v>3278336.87519182</v>
+        <v>3596441.6853742</v>
       </c>
       <c r="P17" s="11" t="n">
-        <v>3836274.27274109</v>
+        <v>4214933.60975031</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -3287,63 +3287,63 @@
       </c>
       <c r="B18" s="18" t="n">
         <f aca="false">IF(B16=0,0,B13*12/B16)</f>
-        <v>0.0493153406405304</v>
+        <v>0.054481879716175</v>
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">IF(C16=0,0,C13*12/C16)</f>
-        <v>0.0569824715890332</v>
+        <v>0.0620453852565179</v>
       </c>
       <c r="D18" s="18" t="n">
         <f aca="false">IF(D16=0,0,D13*12/D16)</f>
-        <v>0.0621819052463801</v>
+        <v>0.067205129723063</v>
       </c>
       <c r="E18" s="18" t="n">
         <f aca="false">IF(E16=0,0,E13*12/E16)</f>
-        <v>0.0958863820595571</v>
+        <v>0.094982545947164</v>
       </c>
       <c r="F18" s="18" t="n">
         <f aca="false">IF(F16=0,0,F13*12/F16)</f>
-        <v>0.102552286442092</v>
+        <v>0.101499896306209</v>
       </c>
       <c r="G18" s="18" t="n">
         <f aca="false">IF(G16=0,0,G13*12/G16)</f>
-        <v>0.109016005559009</v>
+        <v>0.110334955140929</v>
       </c>
       <c r="H18" s="18" t="n">
         <f aca="false">IF(H16=0,0,H13*12/H16)</f>
-        <v>0.119257726280563</v>
+        <v>0.120446152321112</v>
       </c>
       <c r="I18" s="18" t="n">
         <f aca="false">IF(I16=0,0,I13*12/I16)</f>
-        <v>0.128007097652119</v>
+        <v>0.129183448731571</v>
       </c>
       <c r="J18" s="18" t="n">
         <f aca="false">IF(J16=0,0,J13*12/J16)</f>
-        <v>0.135841790877391</v>
+        <v>0.137502084425629</v>
       </c>
       <c r="K18" s="18" t="n">
         <f aca="false">IF(K16=0,0,K13*12/K16)</f>
-        <v>0.144928503206976</v>
+        <v>0.144325695422724</v>
       </c>
       <c r="L18" s="18" t="n">
         <f aca="false">IF(L16=0,0,L13*12/L16)</f>
-        <v>0.205379914192687</v>
+        <v>0.200481283278355</v>
       </c>
       <c r="M18" s="18" t="n">
         <f aca="false">IF(M16=0,0,M13*12/M16)</f>
-        <v>0.21170164641489</v>
+        <v>0.207155917689073</v>
       </c>
       <c r="N18" s="18" t="n">
         <f aca="false">IF(N16=0,0,N13*12/N16)</f>
-        <v>0.217781023218544</v>
+        <v>0.213518697398053</v>
       </c>
       <c r="O18" s="18" t="n">
         <f aca="false">IF(O16=0,0,O13*12/O16)</f>
-        <v>0.227637324498953</v>
+        <v>0.223370875566416</v>
       </c>
       <c r="P18" s="18" t="n">
         <f aca="false">IF(P16=0,0,P13*12/P16)</f>
-        <v>0.236999208545393</v>
+        <v>0.232749239282107</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="6" t="s">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="B19" s="17" t="str">
         <f aca="false">IF(B10=0,"-",IF(B17&gt;=B10,"yes","no - needs a note"))</f>
-        <v>yes</v>
+        <v>no - needs a note</v>
       </c>
       <c r="C19" s="17" t="str">
         <f aca="false">IF(C10=0,"-",IF(C17&gt;=C10,"yes","no - needs a note"))</f>
